--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
@@ -5214,7 +5214,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
@@ -5214,7 +5214,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
@@ -5214,7 +5214,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250930_171455.xlsx
@@ -5214,7 +5214,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
